--- a/data/trans_dic/Q45B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,96</t>
+          <t>1,22; 3,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,67</t>
+          <t>2,16; 5,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,72</t>
+          <t>0,47; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 15,43</t>
+          <t>9,85; 15,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 13,04</t>
+          <t>7,38; 13,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,01</t>
+          <t>3,67; 8,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,82</t>
+          <t>5,65; 8,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,58</t>
+          <t>5,04; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,91</t>
+          <t>2,31; 4,84</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,29</t>
+          <t>2,38; 5,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,16</t>
+          <t>2,24; 5,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,98</t>
+          <t>1,45; 3,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 21,71</t>
+          <t>15,49; 21,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,07; 21,47</t>
+          <t>15,05; 21,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,9</t>
+          <t>6,44; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 12,08</t>
+          <t>8,98; 12,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,06</t>
+          <t>8,69; 12,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,01</t>
+          <t>4,32; 6,92</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,44</t>
+          <t>1,2; 3,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,48</t>
+          <t>1,83; 4,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,36</t>
+          <t>0,16; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,03</t>
+          <t>5,19; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,2</t>
+          <t>6,04; 10,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,51</t>
+          <t>2,46; 5,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,71</t>
+          <t>3,62; 6,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,6</t>
+          <t>4,21; 6,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,1</t>
+          <t>1,52; 3,14</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,8</t>
+          <t>0,39; 2,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,76</t>
+          <t>1,54; 4,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,17; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,17</t>
+          <t>3,27; 7,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,19</t>
+          <t>3,39; 7,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,74</t>
+          <t>1,9; 4,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,3</t>
+          <t>2,1; 4,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,29</t>
+          <t>2,88; 5,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,72</t>
+          <t>1,24; 2,88</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,6</t>
+          <t>0,66; 3,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,36</t>
+          <t>0,26; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,09</t>
+          <t>1,06; 4,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,44</t>
+          <t>0,76; 3,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,24</t>
+          <t>0,69; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,04</t>
+          <t>1,11; 3,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,53</t>
+          <t>0,83; 2,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,67</t>
+          <t>0,36; 1,66</t>
         </is>
       </c>
     </row>
@@ -1228,42 +1228,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,91</t>
+          <t>0,28; 2,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,35</t>
+          <t>0,56; 3,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,01</t>
+          <t>0,85; 5,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,14</t>
+          <t>0,46; 2,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,09</t>
+          <t>0,7; 3,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,28</t>
+          <t>1,11; 4,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,09</t>
+          <t>0,85; 3,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,53</t>
+          <t>1,52; 2,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,12</t>
+          <t>1,98; 3,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,37</t>
+          <t>0,67; 1,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,74</t>
+          <t>6,95; 8,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,4</t>
+          <t>6,52; 8,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,13</t>
+          <t>2,98; 4,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,53</t>
+          <t>4,44; 5,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,59</t>
+          <t>4,49; 5,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,65</t>
+          <t>1,95; 2,64</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5621; 19560</t>
+          <t>6019; 19462</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9697; 25646</t>
+          <t>9767; 25338</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1969; 11322</t>
+          <t>1974; 11983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45446; 72119</t>
+          <t>46054; 72561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31326; 55804</t>
+          <t>31608; 56466</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14525; 31705</t>
+          <t>14540; 32099</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54441; 84796</t>
+          <t>54343; 86250</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45241; 75542</t>
+          <t>44398; 73333</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19328; 39857</t>
+          <t>18726; 39343</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17515; 38897</t>
+          <t>17500; 39980</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15349; 35302</t>
+          <t>15331; 35117</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8502; 23402</t>
+          <t>8511; 23477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97949; 135812</t>
+          <t>96858; 136538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91810; 130812</t>
+          <t>91715; 128250</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36676; 61426</t>
+          <t>36264; 63125</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120081; 164414</t>
+          <t>122221; 166535</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112806; 155944</t>
+          <t>112458; 158478</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50651; 80727</t>
+          <t>49807; 79721</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7282; 21940</t>
+          <t>7671; 21436</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12025; 30483</t>
+          <t>12439; 30631</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1016; 9062</t>
+          <t>1047; 9839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35090; 62273</t>
+          <t>35773; 62901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42733; 72069</t>
+          <t>42718; 71086</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16845; 36284</t>
+          <t>16211; 35334</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47138; 75830</t>
+          <t>48066; 80696</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58362; 91596</t>
+          <t>58397; 93112</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20530; 41112</t>
+          <t>20158; 41592</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2295; 14532</t>
+          <t>2042; 14721</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10463; 29033</t>
+          <t>9376; 28066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1107; 10624</t>
+          <t>1107; 10856</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16472; 36946</t>
+          <t>16884; 36176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20640; 44171</t>
+          <t>20799; 45770</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11359; 30565</t>
+          <t>12237; 31140</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21821; 44464</t>
+          <t>21737; 45214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36051; 64818</t>
+          <t>35248; 64108</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15646; 35027</t>
+          <t>15978; 37161</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2474; 13906</t>
+          <t>2555; 13362</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1131; 10138</t>
+          <t>1134; 10498</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2156</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3856; 16533</t>
+          <t>4284; 17634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3352; 15356</t>
+          <t>3368; 16511</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3450; 16053</t>
+          <t>3415; 16067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7668; 24027</t>
+          <t>8806; 25144</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7378; 22106</t>
+          <t>7292; 21365</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3425; 16170</t>
+          <t>3455; 16131</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5840</t>
+          <t>0; 5695</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7430</t>
+          <t>0; 6489</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>960; 9690</t>
+          <t>948; 8878</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1879; 11499</t>
+          <t>1910; 11491</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3534; 17706</t>
+          <t>3007; 18280</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5161</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3621; 13601</t>
+          <t>2953; 13787</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4040; 20460</t>
+          <t>4665; 19939</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1942; 10791</t>
+          <t>1891; 10842</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1822</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6429</t>
+          <t>0; 7205</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7117</t>
+          <t>0; 9612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4326; 16599</t>
+          <t>4285; 16389</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6758</t>
+          <t>0; 8507</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5478; 19625</t>
+          <t>5419; 19847</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2089</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49328; 82988</t>
+          <t>49932; 83563</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67959; 106551</t>
+          <t>67604; 107270</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21737; 46443</t>
+          <t>22738; 44824</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>233817; 295437</t>
+          <t>234755; 298441</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>231049; 297812</t>
+          <t>231100; 295831</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>103962; 145822</t>
+          <t>105302; 147208</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>292503; 368021</t>
+          <t>295689; 368387</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>315059; 389265</t>
+          <t>312254; 388136</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>133144; 182921</t>
+          <t>134776; 182516</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q45B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,94</t>
+          <t>1,17; 4,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,6</t>
+          <t>2,27; 5,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,88</t>
+          <t>0,47; 2,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 15,52</t>
+          <t>9,83; 15,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 13,19</t>
+          <t>7,42; 13,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,11</t>
+          <t>3,9; 8,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,97</t>
+          <t>5,88; 8,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,33</t>
+          <t>5,14; 8,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,84</t>
+          <t>2,39; 4,86</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,44</t>
+          <t>2,33; 5,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,13</t>
+          <t>2,16; 5,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,99</t>
+          <t>1,38; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,49; 21,83</t>
+          <t>15,44; 21,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,05; 21,05</t>
+          <t>15,0; 21,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,2</t>
+          <t>6,43; 10,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,24</t>
+          <t>8,95; 12,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 12,25</t>
+          <t>8,75; 12,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,92</t>
+          <t>4,18; 6,85</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,36</t>
+          <t>1,29; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,5</t>
+          <t>1,85; 4,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,48</t>
+          <t>0,15; 1,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,12</t>
+          <t>5,02; 9,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,06</t>
+          <t>5,71; 9,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,37</t>
+          <t>2,55; 5,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,07</t>
+          <t>3,49; 5,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,71</t>
+          <t>4,29; 6,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,14</t>
+          <t>1,44; 3,03</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,84</t>
+          <t>0,4; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,6</t>
+          <t>1,59; 4,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,68</t>
+          <t>0,17; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,02</t>
+          <t>3,32; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,46</t>
+          <t>3,39; 7,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,83</t>
+          <t>1,91; 4,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,37</t>
+          <t>2,09; 4,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,24</t>
+          <t>2,78; 5,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,88</t>
+          <t>1,18; 2,74</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,46</t>
+          <t>0,68; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,44</t>
+          <t>0,25; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,36</t>
+          <t>0,97; 4,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,7</t>
+          <t>0,94; 3,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,24</t>
+          <t>0,7; 3,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,18</t>
+          <t>1,1; 3,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,44</t>
+          <t>0,83; 2,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,66</t>
+          <t>0,36; 1,56</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,67</t>
+          <t>0,29; 3,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,35</t>
+          <t>0,56; 3,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,18</t>
+          <t>0,84; 5,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,17</t>
+          <t>0,56; 2,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,01</t>
+          <t>0,75; 3,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,53</t>
+          <t>0,26; 1,53</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,23</t>
+          <t>1,11; 4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,12</t>
+          <t>0,85; 3,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,55</t>
+          <t>1,52; 2,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,14</t>
+          <t>2,04; 3,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,33</t>
+          <t>0,66; 1,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,83</t>
+          <t>6,94; 8,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,35</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,17</t>
+          <t>2,98; 4,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,53</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,58</t>
+          <t>4,52; 5,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,64</t>
+          <t>1,93; 2,63</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6019; 19462</t>
+          <t>5778; 20302</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9767; 25338</t>
+          <t>10261; 27081</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1974; 11983</t>
+          <t>1967; 11090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46054; 72561</t>
+          <t>45966; 72545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31608; 56466</t>
+          <t>31781; 57117</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14540; 32099</t>
+          <t>15445; 32460</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54343; 86250</t>
+          <t>56525; 86254</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44398; 73333</t>
+          <t>45208; 75635</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18726; 39343</t>
+          <t>19386; 39433</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17500; 39980</t>
+          <t>17135; 39322</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15331; 35117</t>
+          <t>14755; 36035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8511; 23477</t>
+          <t>8148; 23036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96858; 136538</t>
+          <t>96595; 135532</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91715; 128250</t>
+          <t>91400; 129232</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36264; 63125</t>
+          <t>36210; 61880</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>122221; 166535</t>
+          <t>121872; 167910</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112458; 158478</t>
+          <t>113245; 156243</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49807; 79721</t>
+          <t>48155; 78880</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7671; 21436</t>
+          <t>8251; 21874</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12439; 30631</t>
+          <t>12593; 30459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1047; 9839</t>
+          <t>978; 10161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35773; 62901</t>
+          <t>34653; 62515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42718; 71086</t>
+          <t>40333; 69531</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16211; 35334</t>
+          <t>16814; 36870</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48066; 80696</t>
+          <t>46385; 78044</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58397; 93112</t>
+          <t>59549; 92343</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20158; 41592</t>
+          <t>19087; 40132</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2042; 14721</t>
+          <t>2052; 14523</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9376; 28066</t>
+          <t>9705; 27409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1107; 10856</t>
+          <t>1093; 10352</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16884; 36176</t>
+          <t>17129; 36260</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20799; 45770</t>
+          <t>20795; 45707</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12237; 31140</t>
+          <t>12289; 31512</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21737; 45214</t>
+          <t>21677; 45039</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35248; 64108</t>
+          <t>34057; 63920</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15978; 37161</t>
+          <t>15234; 35316</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2555; 13362</t>
+          <t>2635; 14470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1134; 10498</t>
+          <t>1076; 10647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2417,32 +2417,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4284; 17634</t>
+          <t>3938; 16701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3368; 16511</t>
+          <t>4188; 15882</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3415; 16067</t>
+          <t>3470; 17113</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8806; 25144</t>
+          <t>8686; 25098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7292; 21365</t>
+          <t>7222; 21188</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3455; 16131</t>
+          <t>3452; 15114</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5695</t>
+          <t>0; 6003</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6489</t>
+          <t>0; 7384</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>948; 8878</t>
+          <t>963; 10522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1910; 11491</t>
+          <t>1922; 11785</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3007; 18280</t>
+          <t>2979; 18186</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>0; 5026</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2953; 13787</t>
+          <t>3547; 13647</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4665; 19939</t>
+          <t>4956; 21204</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1891; 10842</t>
+          <t>1871; 10793</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 8100</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 9612</t>
+          <t>0; 7265</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4285; 16389</t>
+          <t>4320; 16531</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 8507</t>
+          <t>0; 7642</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5419; 19847</t>
+          <t>5424; 19325</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49932; 83563</t>
+          <t>49774; 82123</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67604; 107270</t>
+          <t>69767; 106528</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22738; 44824</t>
+          <t>22425; 43031</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>234755; 298441</t>
+          <t>234665; 299743</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>231100; 295831</t>
+          <t>232067; 295192</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>105302; 147208</t>
+          <t>105092; 146124</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>295689; 368387</t>
+          <t>291859; 361735</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>312254; 388136</t>
+          <t>314296; 388280</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>134776; 182516</t>
+          <t>133241; 182052</t>
         </is>
       </c>
     </row>
